--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.D. BASKET GLOBALCAJA QUINTANAR.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.D. BASKET GLOBALCAJA QUINTANAR.xlsx
@@ -565,13 +565,13 @@
         <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>133.7477</v>
+        <v>108.7931</v>
       </c>
       <c r="E2" t="n">
-        <v>95.1463</v>
+        <v>78.2961</v>
       </c>
       <c r="F2" t="n">
-        <v>38.6009</v>
+        <v>30.4969</v>
       </c>
       <c r="G2" t="n">
         <v>49.0238</v>
@@ -610,13 +610,13 @@
         <v>55.4129</v>
       </c>
       <c r="S2" t="n">
-        <v>42.8422</v>
+        <v>17.8878</v>
       </c>
       <c r="T2" t="n">
-        <v>24.4233</v>
+        <v>7.5724</v>
       </c>
       <c r="U2" t="n">
-        <v>18.4193</v>
+        <v>10.3152</v>
       </c>
       <c r="V2" t="n">
         <v>32.8067</v>
@@ -643,13 +643,13 @@
         <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>35.7713</v>
+        <v>28.2397</v>
       </c>
       <c r="E3" t="n">
-        <v>28.6514</v>
+        <v>23.2531</v>
       </c>
       <c r="F3" t="n">
-        <v>7.119800000000001</v>
+        <v>4.985799999999999</v>
       </c>
       <c r="G3" t="n">
         <v>16.8394</v>
@@ -688,13 +688,13 @@
         <v>32.8233</v>
       </c>
       <c r="S3" t="n">
-        <v>11.3869</v>
+        <v>3.8548</v>
       </c>
       <c r="T3" t="n">
-        <v>4.4593</v>
+        <v>-0.9390999999999998</v>
       </c>
       <c r="U3" t="n">
-        <v>6.9276</v>
+        <v>4.794</v>
       </c>
       <c r="V3" t="n">
         <v>-8.8666</v>
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>30.7082</v>
+        <v>26.1702</v>
       </c>
       <c r="E4" t="n">
-        <v>8.1144</v>
+        <v>6.308599999999998</v>
       </c>
       <c r="F4" t="n">
-        <v>22.594</v>
+        <v>19.8617</v>
       </c>
       <c r="G4" t="n">
         <v>-3.6653</v>
@@ -766,13 +766,13 @@
         <v>45.3734</v>
       </c>
       <c r="S4" t="n">
-        <v>10.6752</v>
+        <v>6.1376</v>
       </c>
       <c r="T4" t="n">
-        <v>3.0514</v>
+        <v>1.2457</v>
       </c>
       <c r="U4" t="n">
-        <v>7.6236</v>
+        <v>4.8919</v>
       </c>
       <c r="V4" t="n">
         <v>6.5143</v>
@@ -799,13 +799,13 @@
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>19.9707</v>
+        <v>17.9007</v>
       </c>
       <c r="E5" t="n">
-        <v>9.0985</v>
+        <v>7.147500000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>10.8721</v>
+        <v>10.7532</v>
       </c>
       <c r="G5" t="n">
         <v>0.1491000000000002</v>
@@ -844,13 +844,13 @@
         <v>20.8525</v>
       </c>
       <c r="S5" t="n">
-        <v>4.0212</v>
+        <v>1.9512</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0361</v>
+        <v>0.08499999999999996</v>
       </c>
       <c r="U5" t="n">
-        <v>1.9852</v>
+        <v>1.8663</v>
       </c>
       <c r="V5" t="n">
         <v>2.2849</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ANDRADE ROSSI</t>
+          <t>G. ZALAZAR RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>5.937599999999999</v>
+        <v>15.8682</v>
       </c>
       <c r="E6" t="n">
-        <v>11.609</v>
+        <v>10.8745</v>
       </c>
       <c r="F6" t="n">
-        <v>-5.6713</v>
+        <v>4.993499999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>10.806</v>
+        <v>9.9855</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7869000000000005</v>
+        <v>6.039900000000002</v>
       </c>
       <c r="I6" t="n">
-        <v>10.019</v>
+        <v>3.945500000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>38.23560000000001</v>
+        <v>44.5424</v>
       </c>
       <c r="K6" t="n">
-        <v>17.629</v>
+        <v>25.5779</v>
       </c>
       <c r="L6" t="n">
-        <v>20.6071</v>
+        <v>18.9644</v>
       </c>
       <c r="M6" t="n">
-        <v>-27.4299</v>
+        <v>-34.557</v>
       </c>
       <c r="N6" t="n">
-        <v>-16.8421</v>
+        <v>-19.5379</v>
       </c>
       <c r="O6" t="n">
-        <v>-10.5875</v>
+        <v>-15.0192</v>
       </c>
       <c r="P6" t="n">
-        <v>7.1436</v>
+        <v>-4.440892098500626e-16</v>
       </c>
       <c r="Q6" t="n">
-        <v>-30.3135</v>
+        <v>-53.483</v>
       </c>
       <c r="R6" t="n">
-        <v>37.4571</v>
+        <v>53.4825</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.737</v>
+        <v>-0.7043000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-4.366</v>
+        <v>-4.3555</v>
       </c>
       <c r="U6" t="n">
-        <v>1.6291</v>
+        <v>3.6512</v>
       </c>
       <c r="V6" t="n">
-        <v>-9.275</v>
+        <v>6.5871</v>
       </c>
       <c r="W6" t="n">
-        <v>8.052300000000001</v>
+        <v>24.1702</v>
       </c>
       <c r="X6" t="n">
-        <v>-17.3273</v>
+        <v>-17.5831</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. VALERO PRIETO</t>
+          <t>A. ANDRADE ROSSI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>3.1401</v>
+        <v>10.8048</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9367</v>
+        <v>14.8568</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2033</v>
+        <v>-4.0524</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8256</v>
+        <v>10.806</v>
       </c>
       <c r="H7" t="n">
-        <v>2.186</v>
+        <v>0.7869000000000005</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6397999999999999</v>
+        <v>10.019</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3507</v>
+        <v>38.23560000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0485</v>
+        <v>17.629</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3022</v>
+        <v>20.6071</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5250999999999999</v>
+        <v>-27.4299</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1374</v>
+        <v>-16.8421</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6624</v>
+        <v>-10.5875</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5792</v>
+        <v>7.1436</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-30.3135</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5792</v>
+        <v>37.4571</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2648</v>
+        <v>2.1299</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4139</v>
+        <v>-1.1183</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1492</v>
+        <v>3.2482</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-9.275</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>8.052300000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-17.3273</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. LUJAN MARCOS</t>
+          <t>J. VALERO PRIETO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,67 +1030,67 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>1.682</v>
+        <v>3.5704</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3651</v>
+        <v>3.1435</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3169</v>
+        <v>0.4268</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9248</v>
+        <v>2.8256</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2827</v>
+        <v>2.186</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.642</v>
+        <v>0.6397999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2762</v>
+        <v>3.3507</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6274</v>
+        <v>2.0485</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6488</v>
+        <v>1.3022</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3514</v>
+        <v>-0.5250999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3447</v>
+        <v>0.1374</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0068</v>
+        <v>-0.6624</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4137</v>
+        <v>0.1655</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4136</v>
+        <v>-0.2071</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0001</v>
+        <v>0.3727</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. CEBRIAN TEVAR</t>
+          <t>A. VERA PICAZO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0207</v>
+        <v>1.700900000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0207</v>
+        <v>-0.209799999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1.9108</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0207</v>
+        <v>21.2727</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0207</v>
+        <v>15.3777</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>5.895</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0207</v>
+        <v>40.8272</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0207</v>
+        <v>28.2929</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>12.5338</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-19.5538</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-12.9154</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-6.6389</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-17.9563</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-68.54300000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>50.5865</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-3.4623</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-3.4163</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0.04630000000000023</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.8465</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>30.9223</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-29.0761</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. ZALAZAR RODRIGUEZ</t>
+          <t>J. LUJAN MARCOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.08260000000000245</v>
+        <v>1.5786</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6126999999999994</v>
+        <v>0.2616</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5299999999999994</v>
+        <v>1.3169</v>
       </c>
       <c r="G10" t="n">
-        <v>9.9855</v>
+        <v>-0.9248</v>
       </c>
       <c r="H10" t="n">
-        <v>6.039900000000002</v>
+        <v>-0.2827</v>
       </c>
       <c r="I10" t="n">
-        <v>3.945500000000001</v>
+        <v>-0.642</v>
       </c>
       <c r="J10" t="n">
-        <v>44.5424</v>
+        <v>-1.2762</v>
       </c>
       <c r="K10" t="n">
-        <v>25.5779</v>
+        <v>-0.6274</v>
       </c>
       <c r="L10" t="n">
-        <v>18.9644</v>
+        <v>-0.6488</v>
       </c>
       <c r="M10" t="n">
-        <v>-34.557</v>
+        <v>0.3514</v>
       </c>
       <c r="N10" t="n">
-        <v>-19.5379</v>
+        <v>0.3447</v>
       </c>
       <c r="O10" t="n">
-        <v>-15.0192</v>
+        <v>0.0068</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.440892098500626e-16</v>
+        <v>0.9654</v>
       </c>
       <c r="Q10" t="n">
-        <v>-53.483</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>53.4825</v>
+        <v>0.9654</v>
       </c>
       <c r="S10" t="n">
-        <v>-16.6548</v>
+        <v>0.3103</v>
       </c>
       <c r="T10" t="n">
-        <v>-15.8429</v>
+        <v>0.3101</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8124999999999999</v>
+        <v>0.0001</v>
       </c>
       <c r="V10" t="n">
-        <v>6.5871</v>
+        <v>1.2277</v>
       </c>
       <c r="W10" t="n">
-        <v>24.1702</v>
+        <v>1.2277</v>
       </c>
       <c r="X10" t="n">
-        <v>-17.5831</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. HAJJI SALHI</t>
+          <t>A. CEBRIAN TEVAR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.202</v>
+        <v>0.0207</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6488</v>
+        <v>0.0207</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4468</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2351</v>
+        <v>0.0207</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1379</v>
+        <v>0.0207</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.373</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6488</v>
+        <v>0.0207</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.0207</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6488</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4137</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1379</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2758</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0331</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0331</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. TEVAR TEVAR</t>
+          <t>A. HAJJI SALHI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4148999999999999</v>
+        <v>-0.0489</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9368000000000001</v>
+        <v>-0.5454</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5220999999999999</v>
+        <v>0.4965</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.016</v>
+        <v>-0.2351</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5032000000000001</v>
+        <v>0.1379</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5191</v>
+        <v>-0.373</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6154000000000001</v>
+        <v>-0.6488</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6415</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2569</v>
+        <v>-0.6488</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4005</v>
+        <v>0.4137</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1383</v>
+        <v>0.1379</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2622</v>
+        <v>0.2758</v>
       </c>
       <c r="P12" t="n">
-        <v>9.999999999998899e-05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9655</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.05519999999999992</v>
+        <v>0.1862</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3584</v>
+        <v>0.1034</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4135</v>
+        <v>0.0828</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3709</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.8475000000000004</v>
+        <v>-0.3032999999999997</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.272800000000002</v>
+        <v>-6.540699999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4252</v>
+        <v>6.237399999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-13.7528</v>
@@ -1468,13 +1468,13 @@
         <v>49.235</v>
       </c>
       <c r="S13" t="n">
-        <v>3.605500000000001</v>
+        <v>4.1499</v>
       </c>
       <c r="T13" t="n">
-        <v>4.1538</v>
+        <v>0.8861000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5482000000000002</v>
+        <v>3.2642</v>
       </c>
       <c r="V13" t="n">
         <v>-2.0922</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. GARRIDO PARDO</t>
+          <t>M. TEVAR TEVAR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.0433</v>
+        <v>-0.8285000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.7077</v>
+        <v>-1.3505</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3355</v>
+        <v>0.522</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6711</v>
+        <v>-1.016</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.000199999999999978</v>
+        <v>0.5032000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6715</v>
+        <v>-1.5191</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5335999999999999</v>
+        <v>-0.6154000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>0.6415</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5335999999999999</v>
+        <v>-1.2569</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1377</v>
+        <v>-0.4005</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.000199999999999978</v>
+        <v>-0.1383</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1379</v>
+        <v>-0.2622</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7723</v>
+        <v>9.999999999998899e-05</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1931</v>
+        <v>0.9655</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6565</v>
+        <v>-0.4688</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.276</v>
+        <v>-0.05530000000000002</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3804999999999999</v>
+        <v>-0.4135</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2856</v>
+        <v>0.6565</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2856</v>
+        <v>0.3709</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. CEBRIAN SOLER</t>
+          <t>F. GARRIDO PARDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,43 +1576,43 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.8572</v>
+        <v>-0.9937</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.9216</v>
+        <v>-0.7077</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9356</v>
+        <v>-0.2859</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.9732</v>
+        <v>0.6711</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.000199999999999978</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.4627</v>
+        <v>0.6715</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.2969</v>
+        <v>0.5335999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0414</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.3383</v>
+        <v>0.5335999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6764</v>
+        <v>0.1377</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.552</v>
+        <v>-0.000199999999999978</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1244</v>
+        <v>0.1379</v>
       </c>
       <c r="P15" t="n">
         <v>-0.7723</v>
@@ -1624,28 +1624,28 @@
         <v>0.1931</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7834000000000001</v>
+        <v>-0.6069</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3311</v>
+        <v>-0.276</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4523</v>
+        <v>-0.3309</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3282</v>
+        <v>-0.2856</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3282</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. BALDERAS MARTÍN</t>
+          <t>J. CEBRIAN SOLER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>-11.0425</v>
+        <v>-3.398</v>
       </c>
       <c r="E16" t="n">
-        <v>-13.3736</v>
+        <v>-2.6113</v>
       </c>
       <c r="F16" t="n">
-        <v>2.330900000000001</v>
+        <v>-0.7867000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.253</v>
+        <v>-1.9732</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6465</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-6.8992</v>
+        <v>-1.4627</v>
       </c>
       <c r="J16" t="n">
-        <v>4.2478</v>
+        <v>-1.2969</v>
       </c>
       <c r="K16" t="n">
-        <v>8.2056</v>
+        <v>0.0414</v>
       </c>
       <c r="L16" t="n">
-        <v>-3.9576</v>
+        <v>-1.3383</v>
       </c>
       <c r="M16" t="n">
-        <v>-9.5007</v>
+        <v>-0.6764</v>
       </c>
       <c r="N16" t="n">
-        <v>-6.5591</v>
+        <v>-0.552</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.9416</v>
+        <v>-0.1244</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5447</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q16" t="n">
-        <v>-16.6049</v>
+        <v>-0.9654</v>
       </c>
       <c r="R16" t="n">
-        <v>18.1494</v>
+        <v>0.1931</v>
       </c>
       <c r="S16" t="n">
-        <v>-5.450299999999999</v>
+        <v>-0.3241000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-4.4441</v>
+        <v>-0.02079999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0062</v>
+        <v>-0.3032</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.8841</v>
+        <v>-0.3282</v>
       </c>
       <c r="W16" t="n">
-        <v>3.4273</v>
+        <v>-0.3282</v>
       </c>
       <c r="X16" t="n">
-        <v>-5.311500000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. VERA PICAZO</t>
+          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>-15.167</v>
+        <v>-4.3239</v>
       </c>
       <c r="E17" t="n">
-        <v>-9.352599999999999</v>
+        <v>-5.249700000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.8145</v>
+        <v>0.9254999999999998</v>
       </c>
       <c r="G17" t="n">
-        <v>21.2727</v>
+        <v>-16.6196</v>
       </c>
       <c r="H17" t="n">
-        <v>15.3777</v>
+        <v>-5.2389</v>
       </c>
       <c r="I17" t="n">
-        <v>5.895</v>
+        <v>-11.3808</v>
       </c>
       <c r="J17" t="n">
-        <v>40.8272</v>
+        <v>-3.718</v>
       </c>
       <c r="K17" t="n">
-        <v>28.2929</v>
+        <v>4.0834</v>
       </c>
       <c r="L17" t="n">
-        <v>12.5338</v>
+        <v>-7.801200000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-19.5538</v>
+        <v>-12.9017</v>
       </c>
       <c r="N17" t="n">
-        <v>-12.9154</v>
+        <v>-9.3222</v>
       </c>
       <c r="O17" t="n">
-        <v>-6.6389</v>
+        <v>-3.5795</v>
       </c>
       <c r="P17" t="n">
-        <v>-17.9563</v>
+        <v>19.887</v>
       </c>
       <c r="Q17" t="n">
-        <v>-68.54300000000001</v>
+        <v>-9.654</v>
       </c>
       <c r="R17" t="n">
-        <v>50.5865</v>
+        <v>29.5408</v>
       </c>
       <c r="S17" t="n">
-        <v>-20.3304</v>
+        <v>-2.766</v>
       </c>
       <c r="T17" t="n">
-        <v>-12.5592</v>
+        <v>-2.7991</v>
       </c>
       <c r="U17" t="n">
-        <v>-7.771</v>
+        <v>0.03279999999999997</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8465</v>
+        <v>-4.8253</v>
       </c>
       <c r="W17" t="n">
-        <v>30.9223</v>
+        <v>10.9214</v>
       </c>
       <c r="X17" t="n">
-        <v>-29.0761</v>
+        <v>-15.7467</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
+          <t>J. BALDERAS MARTÍN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>-18.2303</v>
+        <v>-6.5923</v>
       </c>
       <c r="E18" t="n">
-        <v>-13.8199</v>
+        <v>-10.3053</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.4104</v>
+        <v>3.713099999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-16.6196</v>
+        <v>-5.253</v>
       </c>
       <c r="H18" t="n">
-        <v>-5.2389</v>
+        <v>1.6465</v>
       </c>
       <c r="I18" t="n">
-        <v>-11.3808</v>
+        <v>-6.8992</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.718</v>
+        <v>4.2478</v>
       </c>
       <c r="K18" t="n">
-        <v>4.0834</v>
+        <v>8.2056</v>
       </c>
       <c r="L18" t="n">
-        <v>-7.801200000000001</v>
+        <v>-3.9576</v>
       </c>
       <c r="M18" t="n">
-        <v>-12.9017</v>
+        <v>-9.5007</v>
       </c>
       <c r="N18" t="n">
-        <v>-9.3222</v>
+        <v>-6.5591</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.5795</v>
+        <v>-2.9416</v>
       </c>
       <c r="P18" t="n">
-        <v>19.887</v>
+        <v>1.5447</v>
       </c>
       <c r="Q18" t="n">
-        <v>-9.654</v>
+        <v>-16.6049</v>
       </c>
       <c r="R18" t="n">
-        <v>29.5408</v>
+        <v>18.1494</v>
       </c>
       <c r="S18" t="n">
-        <v>-16.6721</v>
+        <v>-0.9999000000000002</v>
       </c>
       <c r="T18" t="n">
-        <v>-11.3696</v>
+        <v>-1.376</v>
       </c>
       <c r="U18" t="n">
-        <v>-5.3026</v>
+        <v>0.3759999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-4.8253</v>
+        <v>-1.8841</v>
       </c>
       <c r="W18" t="n">
-        <v>10.9214</v>
+        <v>3.4273</v>
       </c>
       <c r="X18" t="n">
-        <v>-15.7467</v>
+        <v>-5.311500000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1891,22 +1891,22 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>180.091</v>
+        <v>198.1587</v>
       </c>
       <c r="E19" t="n">
-        <v>110.2956</v>
+        <v>116.642</v>
       </c>
       <c r="F19" t="n">
-        <v>69.79470000000001</v>
+        <v>81.51509999999999</v>
       </c>
       <c r="G19" t="n">
         <v>68.1541</v>
       </c>
       <c r="H19" t="n">
-        <v>32.0604</v>
+        <v>32.06040000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>36.09460000000001</v>
+        <v>36.0946</v>
       </c>
       <c r="J19" t="n">
         <v>274.5742</v>
@@ -1924,7 +1924,7 @@
         <v>-130.156</v>
       </c>
       <c r="O19" t="n">
-        <v>-76.26389999999999</v>
+        <v>-76.26390000000001</v>
       </c>
       <c r="P19" t="n">
         <v>78.197</v>
@@ -1936,13 +1936,13 @@
         <v>395.8097</v>
       </c>
       <c r="S19" t="n">
-        <v>9.3733</v>
+        <v>27.4409</v>
       </c>
       <c r="T19" t="n">
-        <v>-10.7069</v>
+        <v>-4.3608</v>
       </c>
       <c r="U19" t="n">
-        <v>20.0804</v>
+        <v>31.8015</v>
       </c>
       <c r="V19" t="n">
         <v>24.3667</v>
